--- a/火车乘车记录.xlsx
+++ b/火车乘车记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\火车乘车记录\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{937C899A-EA92-418A-979C-CEA5F853BA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4901077-17BC-462F-9DC1-FA6D04101328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="148">
   <si>
     <t>日期</t>
   </si>
@@ -46,12 +46,69 @@
     <t>担当路局</t>
   </si>
   <si>
+    <t>2023.7.27</t>
+  </si>
+  <si>
+    <t>南京南</t>
+  </si>
+  <si>
+    <t>兰州西</t>
+  </si>
+  <si>
+    <t>G1970</t>
+  </si>
+  <si>
+    <t>CRH380BL</t>
+  </si>
+  <si>
+    <t>上海虹桥</t>
+  </si>
+  <si>
+    <t>上海局</t>
+  </si>
+  <si>
+    <t>2023.8.3</t>
+  </si>
+  <si>
+    <t>大通西</t>
+  </si>
+  <si>
+    <t>西宁</t>
+  </si>
+  <si>
+    <t>D9914</t>
+  </si>
+  <si>
+    <t>CRH5G</t>
+  </si>
+  <si>
+    <t>门源</t>
+  </si>
+  <si>
+    <t>青藏公司</t>
+  </si>
+  <si>
     <t>2023.8.4</t>
   </si>
   <si>
+    <t>西安北</t>
+  </si>
+  <si>
     <t>郑州东</t>
   </si>
   <si>
+    <t>G56</t>
+  </si>
+  <si>
+    <t>CR400BF重联</t>
+  </si>
+  <si>
+    <t>北京西</t>
+  </si>
+  <si>
+    <t>北京局</t>
+  </si>
+  <si>
     <t>武汉</t>
   </si>
   <si>
@@ -61,18 +118,27 @@
     <t>CR400AF-Z-0212</t>
   </si>
   <si>
-    <t>北京西</t>
-  </si>
-  <si>
     <t>武汉局</t>
   </si>
   <si>
+    <t>2023.8.5</t>
+  </si>
+  <si>
+    <t>杭州西</t>
+  </si>
+  <si>
+    <t>G254</t>
+  </si>
+  <si>
+    <t>CR400BF</t>
+  </si>
+  <si>
+    <t>青岛北</t>
+  </si>
+  <si>
     <t>2023.10.2</t>
   </si>
   <si>
-    <t>南京南</t>
-  </si>
-  <si>
     <t>无锡东</t>
   </si>
   <si>
@@ -85,12 +151,6 @@
     <t>亳州南</t>
   </si>
   <si>
-    <t>上海虹桥</t>
-  </si>
-  <si>
-    <t>上海局</t>
-  </si>
-  <si>
     <t>无锡</t>
   </si>
   <si>
@@ -124,7 +184,7 @@
     <t>2024.6.7</t>
   </si>
   <si>
-    <t>北京</t>
+    <t>北京南</t>
   </si>
   <si>
     <t>G172</t>
@@ -136,9 +196,6 @@
     <t>杭州东</t>
   </si>
   <si>
-    <t>北京南</t>
-  </si>
-  <si>
     <t>2024.6.11</t>
   </si>
   <si>
@@ -148,7 +205,28 @@
     <t>CR400AF-B-2121</t>
   </si>
   <si>
-    <t>北京局</t>
+    <t>2025.8.1</t>
+  </si>
+  <si>
+    <t>香港西九龙</t>
+  </si>
+  <si>
+    <t>深圳北</t>
+  </si>
+  <si>
+    <t>G5616</t>
+  </si>
+  <si>
+    <t>CR400AF-Z</t>
+  </si>
+  <si>
+    <t>广州南</t>
+  </si>
+  <si>
+    <t>G6240</t>
+  </si>
+  <si>
+    <t>CR400BF-Z</t>
   </si>
   <si>
     <t>2025.10.1</t>
@@ -163,9 +241,6 @@
     <t>CRH2B-4101</t>
   </si>
   <si>
-    <t>杭州西</t>
-  </si>
-  <si>
     <t>2025.10.8</t>
   </si>
   <si>
@@ -247,9 +322,6 @@
     <t>CR400BF-S-3251</t>
   </si>
   <si>
-    <t>广州南</t>
-  </si>
-  <si>
     <t>广州局</t>
   </si>
   <si>
@@ -277,6 +349,9 @@
     <t>G1737</t>
   </si>
   <si>
+    <t>CR400BF-Z-3147+CR400BF-Z-5267重联</t>
+  </si>
+  <si>
     <t>宜昌北</t>
   </si>
   <si>
@@ -304,6 +379,9 @@
     <t>G1115</t>
   </si>
   <si>
+    <t>CR400AF-S-2362+CR400AF-S-2367重联</t>
+  </si>
+  <si>
     <t>湛江北</t>
   </si>
   <si>
@@ -340,9 +418,6 @@
     <t>CR400BF-S-3279</t>
   </si>
   <si>
-    <t>深圳北</t>
-  </si>
-  <si>
     <t>2026.8.12</t>
   </si>
   <si>
@@ -388,11 +463,7 @@
     <t>CRH1A-A-1172+CRH1A-A-1248重联</t>
   </si>
   <si>
-    <t>CR400BF-Z-3147+CR400BF-Z-5267重联</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CR400AF-S-2362+CR400AF-S-2367重联</t>
+    <t>广州局</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -793,10 +864,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
@@ -875,62 +948,62 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -938,10 +1011,10 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>35</v>
@@ -950,24 +1023,24 @@
         <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>40</v>
@@ -976,36 +1049,36 @@
         <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -1013,13 +1086,13 @@
     </row>
     <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>49</v>
@@ -1028,507 +1101,663 @@
         <v>50</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>76</v>
+      <c r="B29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
